--- a/emlaw_crawler/CauHoi_BoSung_Kind1-4.xlsx
+++ b/emlaw_crawler/CauHoi_BoSung_Kind1-4.xlsx
@@ -526,7 +526,20 @@
           <t>Kind 1 - Thủ tục quản lý đất đai</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Kết luận: Xã không thể tự đặt thêm điều kiện bắt buộc phải có giấy đăng ký kết hôn, giấy chứng tử hoặc mộ của ông nếu bà là người duy nhất đứng tên trên sổ hồng và đang tự nguyện tặng cho đất cho bố bạn. Giấy khai sinh của bố chủ yếu chỉ cần để chứng minh quan hệ mẹ–con khi xin miễn thuế, lệ phí; việc ông mất tích không làm mất quyền định đoạt tài sản riêng của bà.
+Nếu sổ hồng chỉ ghi tên bà, gia đình nên làm theo hướng hợp đồng tặng cho quyền sử dụng đất từ bà sang bố, có công chứng/chứng thực, sau đó nộp hồ sơ đăng ký biến động tại cơ quan đăng ký đất đai. Hồ sơ trọng tâm là: sổ hồng bản gốc, CCCD của bà và bố, hợp đồng tặng cho, tờ khai thuế/lệ phí và giấy tờ chứng minh mẹ–con.
+Bố bạn đã có giấy khai sinh thì nộp giấy đó. Quan hệ mẹ–con cũng có thể được chứng minh bằng trích lục hộ tịch, dữ liệu dân cư/căn cước hoặc xác nhận của UBND xã nơi cư trú, không chỉ duy nhất bằng giấy khai sinh Điều 6 Nghị định 154/2024/NĐ-CP.
+Vì tặng cho giữa mẹ và con ruột, bố bạn được miễn thuế thu nhập cá nhân và lệ phí trước bạ, nhưng phải có hồ sơ chứng minh quan hệ mẹ–con Điều 4 Luật Thuế thu nhập cá nhân Điều 10 Nghị định 10/2022/NĐ-CP.
+Việc xã đòi giấy kết hôn của ông bà chỉ có thể có lý do nếu họ nghi ngờ mảnh đất là tài sản chung vợ chồng và cần xác định quyền của ông. Tuy nhiên, ông đã mất tích từ thời chiến tranh, không phải vì thế mà bắt buộc gia đình phải tìm được mộ hoặc giấy chứng tử mới được làm thủ tục. Nếu cần xử lý phần tài sản của ông, gia đình có thể làm thủ tục yêu cầu Tòa án tuyên bố ông đã chết khi đáp ứng điều kiện luật định; quyết định của Tòa án là căn cứ hộ tịch và thừa kế, không cần có mộ Điều 71 Bộ luật Dân sự 2015.
+Trước mắt, bạn nên yêu cầu cán bộ xã trả lời rõ bằng phiếu hướng dẫn bổ sung hồ sơ hoặc văn bản nêu căn cứ pháp luật: giấy đăng ký kết hôn, giấy chứng tử và mộ được yêu cầu theo quy định nào. Không nên chỉ nhận yêu cầu miệng. Nếu sổ hồng đứng tên riêng bà và không có tranh chấp, hãy đề nghị tiếp nhận hồ sơ tặng cho; trường hợp bị từ chối, yêu cầu văn bản từ chối để khiếu nại đến người đứng đầu UBND xã hoặc cơ quan đăng ký đất đai.
+[1]. Điều 6, Nghị định 154/2024/NĐ-CP
+[2]. Điều 4, Luật 04/2007/QH12
+[3]. Điều 10, Nghị định 10/2022/NĐ-CP
+[4]. Điều 71, Luật 91/2015/QH13</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="128" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
@@ -541,7 +554,27 @@
           <t>Kind 1 - Thủ tục quản lý đất đai</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Kết luận: Gia đình bạn vẫn có thể được cấp sổ đỏ cho 150 m² nếu phần đất này đủ điều kiện, hồ sơ nguồn gốc đất và nghĩa vụ tài chính đã hoàn thành. Tuy nhiên, phường không thể chỉ “nói miệng” buộc gia đình trả 180 m² đất còn lại để làm đường; nếu Nhà nước thu hồi đất thì phải có hồ sơ, quyết định đúng thẩm quyền và phải giải quyết bồi thường/hỗ trợ theo quy định.
+Việc đã nộp thuế cho hồ sơ 150 m² không tự động làm mất quyền đối với 180 m² còn lại. Nhưng sổ đỏ chỉ ghi diện tích mà cơ quan đăng ký đất đai xác định là đủ điều kiện cấp, dựa vào: giấy tờ giao đất/cấp đất cho ông, bản đồ địa chính, ranh giới thực tế, quy hoạch và tình trạng tranh chấp.
+Phường không phải cơ quan có thẩm quyền tự quyết định cấp hoặc không cấp sổ đỏ cho hộ gia đình. Hiện nay, việc cấp sổ lần đầu cho cá nhân/hộ gia đình thuộc cơ quan đăng ký đất đai hoặc chi nhánh của cơ quan này theo phân cấp, không phải chỉ do UBND phường quyết định Điều 136 Luật Đất đai 2024.
+Với 180 m² còn lại, có 3 khả năng chính:
+Vẫn là đất gia đình đang sử dụng hợp pháp: Gia đình có quyền đề nghị đo đạc, xác minh nguồn gốc và xin cấp sổ cho toàn bộ 330 m², hoặc xin cấp riêng phần đủ điều kiện. Việc ông là lão thành cách mạng là thông tin rất quan trọng, nhưng cần tìm giấy tờ cụ thể như: quyết định giao/cấp đất, giấy phân nhà đất, giấy kê khai nhà đất, biên lai thuế cũ, xác nhận quá trình sử dụng đất, bản đồ/sổ mục kê.
+Phần 180 m² nằm trong quy hoạch đường: Quy hoạch chưa đồng nghĩa với việc đất đã bị thu hồi. Gia đình vẫn có quyền sử dụng đất cho đến khi có quyết định thu hồi đất hợp pháp. Khi thu hồi để làm đường, Nhà nước phải thực hiện đúng căn cứ, trình tự, thông báo, kiểm đếm, lập phương án bồi thường/hỗ trợ; không thể yêu cầu gia đình ký “trả đất” mà không nêu rõ căn cứ và phương án quyền lợi. Việc thu hồi sai trường hợp, sai thẩm quyền, sai trình tự hoặc xác định sai diện tích là hành vi vi phạm Điều 109 Nghị định 102/2024/NĐ-CP.
+180 m² không được công nhận do nguồn gốc hoặc ranh giới: Cơ quan giải quyết phải trả lời bằng văn bản, ghi rõ lý do, diện tích, vị trí, căn cứ pháp lý và hướng xử lý. Không được chỉ thông báo miệng rằng “không ký trả đất thì không làm được sổ”.
+Gia đình nên làm ngay một văn bản đề nghị cung cấp thông tin và giải quyết hồ sơ, gửi UBND phường và Chi nhánh Văn phòng đăng ký đất đai nơi có đất, yêu cầu:
+Cho sao/chụp hồ sơ cấp sổ năm 2022 và hồ sơ 330 m² năm 2025;
+Trả lời bằng văn bản vì sao chỉ giải quyết 150 m²;
+Cung cấp bản đồ, trích đo và thông tin quy hoạch đường đối với 180 m²;
+Nếu có dự án thu hồi, yêu cầu cung cấp quyết định/chủ trương thu hồi, thông báo thu hồi đất, phạm vi thu hồi và phương án bồi thường, hỗ trợ;
+Xác định rõ 180 m² hiện đứng tên/quản lý bởi ai và căn cứ nào.
+Không nên ký giấy “tự nguyện trả đất”, “hiến đất” hoặc giấy từ chối quyền sử dụng 180 m² khi chưa nhận được bản dự thảo, chưa biết chính xác diện tích/vị trí bị ảnh hưởng và chưa rõ có bồi thường hay không. Nếu gia đình tự nguyện hiến đất thì về sau rất khó yêu cầu bồi thường cho phần đã tự nguyện giao.
+Bạn cần giữ toàn bộ giấy nộp thuế, phiếu tiếp nhận hồ sơ, thông báo nghĩa vụ tài chính và giấy tờ về việc Nhà nước cấp đất cho ông. Nếu phường tiếp tục gắn điều kiện “phải trả 180 m² mới cấp sổ 150 m²”, hãy yêu cầu họ trả lời bằng văn bản để gia đình có căn cứ khiếu nại hoặc đề nghị cơ quan cấp tỉnh kiểm tra.
+[1]. Điều 136, Luật 31/2024/QH15
+[2]. Điều 109, Nghị định 102/2024/NĐ-CP</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="48" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -579,6 +612,16 @@
           <t>Kind 1 - Thủ tục quản lý đất đai</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Kết luận: Bạn không thể tự làm thủ tục “đổi tên” đất từ mẹ sang mình chỉ vì bạn là người giám hộ. Việc tặng cho hoặc chuyển nhượng đất của mẹ chỉ có thể thực hiện khi đó thực sự là giao dịch vì lợi ích của mẹ, có sự đồng ý bằng văn bản của chị gái là người giám sát giám hộ; nếu là chuyển tài sản của mẹ sang cho chính bạn thì có xung đột lợi ích và thường phải cử người giám hộ khác đại diện trong giao dịch.
+Người mất năng lực hành vi dân sự phải do người giám hộ xác lập, thực hiện giao dịch dân sự nhân danh họ. Tuy nhiên, người giám hộ phải quản lý tài sản vì lợi ích của người được giám hộ, không được đem tài sản của mẹ tặng cho mình hoặc giao dịch làm thiệt hại quyền lợi của mẹ Điều 59 Bộ luật Dân sự 2015.
+Với bất động sản của người được giám hộ, việc bán, chuyển nhượng, tặng cho, thế chấp hoặc giao dịch khác phải có sự đồng ý của người giám sát việc giám hộ. Chị gái bạn cần lập văn bản đồng ý rõ nội dung giao dịch; nhưng sự đồng ý này không làm hợp pháp một giao dịch nhằm chuyển tài sản của mẹ cho chính người giám hộ mà không chứng minh được lợi ích của mẹ Điều 59 Bộ luật Dân sự 2015.
+Nếu mẹ có nhu cầu bán đất để lấy tiền chữa bệnh, chăm sóc hoặc bảo đảm sinh hoạt, có thể làm thủ tục chuyển nhượng cho người khác theo giá phù hợp thị trường; tiền thu được phải quản lý, sử dụng cho mẹ. Còn nếu muốn bán/tặng cho chính bạn, nên đề nghị cơ quan có thẩm quyền cử người giám hộ khác hoặc người đại diện phù hợp để tránh việc bạn vừa đại diện cho mẹ vừa là bên nhận tài sản.
+Nếu mẹ qua đời, quyền sử dụng đất sẽ được giải quyết theo di chúc hợp pháp; nếu không có di chúc thì chia thừa kế theo pháp luật cho các hàng thừa kế, không tự động thuộc riêng bạn Điều 650 Bộ luật Dân sự 2015 Điều 651 Bộ luật Dân sự 2015.
+[1]. Điều 59, 650, 651, Luật 91/2015/QH13</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="48" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -591,6 +634,20 @@
           <t>Kind 1 - Thủ tục quản lý đất đai</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Kết luận: Bạn có khả năng được cấp sổ đỏ lần đầu, nhưng chưa thể khẳng định “đủ điều kiện” chỉ từ giấy thanh lý. Trường hợp khu tập thể do nhà máy thanh lý/bố trí cho công nhân thường được xem xét theo quy định về đất do tổ chức bố trí làm nhà ở hoặc thanh lý nhà ở không đúng quy định; yếu tố quyết định là mốc thời điểm sử dụng, không tranh chấp, quy hoạch và nguồn gốc/quyền quản lý đất của nhà máy.
+Nếu nhà máy đã bố trí hoặc thanh lý nhà ở, đất ở cho công nhân trước ngày 01/8/2024, diện tích đất này phải được tổ chức bàn giao cho UBND cấp có thẩm quyền để làm thủ tục cấp giấy cho người đang sử dụng; người được cấp giấy phải thực hiện nghĩa vụ tài chính theo quy định. Khoản 2 Điều 142 Luật Đất đai 2024
+Trường hợp việc thanh lý nhà/đất trước đây không hoàn toàn đúng thủ tục, vẫn có hướng cấp giấy:
+Sử dụng ổn định trước 15/10/1993 và UBND xã/phường xác nhận không tranh chấp: được xem xét cấp giấy đối với diện tích đã giao.
+Sử dụng ổn định từ 15/10/1993 đến trước 01/7/2004: cần không tranh chấp và phù hợp quy hoạch.
+Từ 01/7/2004 đến trước 01/7/2014: cần không tranh chấp, phù hợp quy hoạch; đất ở thường được công nhận trong hạn mức giao đất ở tại địa phương. Điều 140 Luật Đất đai 2024
+Với hồ sơ bạn nêu, giấy thanh lý bản gốc có dấu, hồ sơ kỹ thuật năm 1997 và trích lục năm 2021 là chứng cứ có giá trị để chứng minh nguồn gốc và quá trình sử dụng. Bạn nên chuẩn bị thêm: giấy tờ nộp tiền/thanh lý (nếu có), biên lai thuế nhà đất hoặc xác nhận cư trú, giấy tờ về nhà ở, xác nhận của các hộ liền kề và đặc biệt là xác nhận của UBND phường/xã về thời điểm sử dụng ổn định, hiện trạng không tranh chấp.
+Bạn nộp hồ sơ đăng ký, cấp Giấy chứng nhận lần đầu tại cơ quan đăng ký đất đai thuộc Sở Tài chính tỉnh Quảng Ninh hoặc bộ phận một cửa theo nơi tiếp nhận của địa phương. Cơ quan này sẽ kiểm tra liệu khu đất còn thuộc quyền quản lý của nhà máy/doanh nghiệp, có thuộc quy hoạch phải thu hồi hay không và yêu cầu nhà máy hoặc cơ quan đang quản lý đất thực hiện bàn giao hồ sơ nếu cần.
+Lưu ý: “không tranh chấp” chưa tự động đủ để có sổ. Nếu giấy thanh lý chỉ thanh lý căn nhà mà không thể hiện đất, hoặc nhà máy không có quyền thanh lý/bố trí đất, hồ sơ vẫn có thể được xem xét theo Điều 140 nêu trên, nhưng có thể phải nộp tiền sử dụng đất và bị giới hạn diện tích công nhận. Điều 140 Luật Đất đai 2024
+[1]. Điều 140, 142, Luật 31/2024/QH15</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="48" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
@@ -603,6 +660,21 @@
           <t>Kind 1 - Thủ tục quản lý đất đai</t>
         </is>
       </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Kết luận: Sai lệch tọa độ khoảng 50 cm không đương nhiên làm hồ sơ tách thửa bị từ chối. Tuy nhiên, cơ quan đăng ký đất đai thường sẽ yêu cầu đo đạc, xác định lại ranh giới thực tế và chỉnh lý dữ liệu/bản đồ trước hoặc đồng thời khi tách thửa; nếu không có tranh chấp, không lấn ranh và diện tích vẫn đủ điều kiện tách thì về nguyên tắc vẫn xử lý được.
+Việc “lệch tọa độ” cần phân biệt: nếu chỉ là sai số dữ liệu/bản đồ cũ và ranh đất thực tế ổn định, các hộ liền kề thống nhất, thì đơn vị đo đạc sẽ lập hồ sơ đo đạc chỉnh lý theo hiện trạng. Nếu sự lệch làm chồng lấn sang đất hàng xóm, đất công, hành lang công trình hoặc các hộ không ký xác nhận ranh giới, hồ sơ có thể phải tạm dừng để xác minh, giải quyết tranh chấp.
+Khi kích thước, diện tích có thay đổi vượt sai số, cơ quan chuyên môn phải kiểm tra hồ sơ địa chính, giấy tờ đã cấp; nếu không đủ cơ sở thì đo đạc lại ranh giới tại thực địa. Kết quả phải được thể hiện trong phiếu đo đạc chỉnh lý và có xác nhận của người sử dụng đất, người quản lý đất (nếu có) và Văn phòng đăng ký đất đai/Chi nhánh Văn phòng đăng ký đất đai Điều 17 Thông tư 26/2024/TT-BTNMT.
+Do đó, gia đình nên:
+Đề nghị đơn vị đo đạc kiểm tra nguyên nhân lệch: do hệ tọa độ/bản đồ cũ hay do ranh sử dụng thực tế khác Giấy chứng nhận.
+Cắm mốc, lập bản mô tả ranh giới/mốc giới; nên mời các hộ giáp ranh ký xác nhận để tránh hồ sơ bị yêu cầu bổ sung.
+Nộp hồ sơ tách thửa kèm trích đo địa chính mới tại Chi nhánh Văn phòng đăng ký đất đai nơi có đất. Nếu cần, đề nghị thực hiện chỉnh lý thông tin thửa đất trong cùng hồ sơ.
+Kiểm tra điều kiện diện tích tối thiểu, kích thước cạnh thửa, lối đi và quy hoạch theo quyết định tách thửa của tỉnh/thành phố nơi có đất; đây là điều kiện địa phương nên mỗi nơi có thể khác nhau.
+Trường hợp bản đồ địa chính mới có ranh thể hiện khác Giấy chứng nhận cũ nhưng chưa cấp đổi theo bản đồ mới, ranh giới và diện tích sử dụng đất trước hết được xác định theo Giấy chứng nhận đã cấp Điều 7 Thông tư 10/2024/TT-BTNMT.
+[1]. Điều 17, Thông tư 26/2024/TT-BTNMT
+[2]. Điều 7, Thông tư 10/2024/TT-BTNMT</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="32" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -615,6 +687,16 @@
           <t>Kind 1 - Thủ tục quản lý đất đai</t>
         </is>
       </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Kết luận: Giấy mua bán/giấy tay lập năm 2017 không tự động làm được sổ; vẫn có thể được xem xét nếu nguồn gốc thửa đất hợp pháp, không tranh chấp, phù hợp quy hoạch và việc chuyển nhượng đáp ứng điều kiện pháp luật. Với nhà cấp 4 hiện có, bạn thường cần làm rõ quyền sử dụng đất trước; xin phép xây 2 tầng chỉ khả thi khi đất là đất ở hợp pháp và đáp ứng quy hoạch, chỉ giới xây dựng.
+Giấy tay năm 2017 là giao dịch sau thời điểm pháp luật đã yêu cầu việc chuyển nhượng quyền sử dụng đất phải có công chứng/chứng thực và đăng ký. Vì vậy, nếu bên bán đang đứng tên sổ, cách an toàn nhất là liên hệ bên bán để làm thủ tục chuyển nhượng đúng hình thức; nếu bên bán không hợp tác, cần xem hồ sơ cụ thể để xác định có căn cứ khởi kiện/yêu cầu công nhận giao dịch hay không. Trường hợp đất “không sổ” thì phải kiểm tra nguồn gốc, thời điểm sử dụng đất, vi phạm và tranh chấp; quy định công nhận đất không giấy tờ chủ yếu áp dụng cho quá trình sử dụng đất từ các mốc trước ngày 01/7/2014, nên mua giấy tay năm 2017 không phải là căn cứ độc lập để được cấp sổ Điều 138 Luật Đất đai 2024.
+Về xây 2 tầng: không nên tự xây hoặc tháo nhà cấp 4 trước khi có giấy phép. Hồ sơ xin phép hiện có thể sử dụng giấy chứng nhận hoặc giấy tờ đủ điều kiện cấp giấy chứng nhận; tuy nhiên bạn phải chứng minh đất hợp pháp, đúng mục đích đất ở, không vướng quy hoạch/kế hoạch thu hồi đất và thiết kế phù hợp quy định xây dựng Điều 55 Nghị định 217/2026/NĐ-CP.
+Bạn nên mang các giấy tờ sau đến UBND phường nơi có đất hoặc cơ quan đăng ký đất đai tại TP.HCM để kiểm tra trước: giấy tay 2017; bản sao sổ/giấy tờ nguồn gốc của người bán (nếu có); biên nhận tiền; giấy tờ nhà cấp 4; biên lai thuế; thông tin quy hoạch. Cần kiểm tra riêng thửa đất có phải đất ở, có bị quy hoạch hoặc có phần xây dựng không phép hay không; đây là các yếu tố quyết định có thể cấp sổ và xin phép 2 tầng.
+[1]. Điều 138, Luật 31/2024/QH15
+[2]. Điều 55, Nghị định 217/2026/NĐ-CP</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="64" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
@@ -627,6 +709,41 @@
           <t>Kind 1 - Thủ tục quản lý đất đai</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Kết luận: Làm được, nhưng không phải chỉ “đổi tên sổ”. Cần giải quyết thủ tục thừa kế của ông nội trước, rồi đăng ký sang tên bố bạn và tách thành 3 thửa; có thể đề nghị xử lý trong cùng một hồ sơ nếu địa phương cho phép. Không nên làm “tiểu ngạch” vì dễ phát sinh rủi ro hồ sơ giả, bị từ chối cấp sổ hoặc tranh chấp sau này.
+1. Điều kiện quan trọng nhất
+Ông nội mất có để lại di chúc không? Nếu không có di chúc, người thừa kế hàng thứ nhất gồm: vợ, cha mẹ, con của ông nội. Vì vậy, “các bác đồng thuận” chỉ là một phần; phải xác định đầy đủ những người thuộc hàng thừa kế, kể cả bà nội (nếu còn sống), các con khác của ông nội, và phần tài sản chung của ông bà nếu có. Điều 651 Bộ luật Dân sự 2015
+Nếu mọi người đồng ý để bố bạn nhận toàn bộ quyền sử dụng đất, thường lập văn bản thỏa thuận phân chia di sản hoặc văn bản khai nhận di sản tại tổ chức công chứng. Người có quyền thừa kế nhưng không nhận phần của mình có thể làm văn bản từ chối nhận di sản; việc từ chối phải lập thành văn bản và không nhằm trốn tránh nghĩa vụ tài sản. Điều 620 Bộ luật Dân sự 2015
+Muốn tách được 3 sổ, đất phải đáp ứng diện tích tối thiểu, kích thước cạnh thửa, lối đi, quy hoạch và điều kiện khác theo quy định của tỉnh/thành phố nơi có đất. Đây là phần cần kiểm tra kỹ nhất trước khi công chứng. Điều 220 Luật Đất đai 2024
+2. Cách làm thực tế
+Kiểm tra sổ hiện có, quy hoạch, tình trạng thế chấp/tranh chấp, và hỏi cơ quan đất đai địa phương về điều kiện tách thành 3 thửa.
+Thu thập giấy chứng tử của ông nội; giấy tờ chứng minh quan hệ của toàn bộ người thừa kế; sổ đỏ; CCCD; giấy tờ hôn nhân của ông/bà nếu liên quan.
+Công chứng văn bản thỏa thuận phân chia di sản, xác định bố bạn nhận đất.
+Nộp hồ sơ tại Bộ phận một cửa cấp xã/phường hoặc cơ quan đăng ký đất đai theo quy trình đang áp dụng tại địa phương: đăng ký nhận thừa kế và đề nghị tách thửa/cấp giấy chứng nhận cho 3 thửa.
+Cơ quan chuyên môn đo đạc, lập bản trích đo địa chính nếu cần; cơ quan thuế ra thông báo nghĩa vụ tài chính; nộp xong thì nhận 3 giấy chứng nhận.
+Về nguyên tắc, khi chuyển quyền đối với một phần thửa đất, hồ sơ địa chính sẽ ghi nhận việc tách các thửa mới và việc nhận thừa kế tương ứng. Điều 13 Thông tư 10/2024/TT-BTNMT
+3. Thời gian
+Nếu hồ sơ rõ ràng, không vướng quy hoạch, không thiếu người thừa kế và không cần giải quyết tranh chấp: thường khoảng 3–8 tuần tính cả công chứng, đo đạc, nghĩa vụ tài chính và cấp sổ. Thực tế có thể lâu hơn nếu phải xác minh nguồn gốc đất, niêm yết thừa kế, bổ sung giấy tờ nhân thân hoặc đo đạc lại.
+Đang sáp nhập địa giới không làm mất quyền làm thủ tục. Tuy nhiên, nên nộp tại Bộ phận một cửa nơi thửa đất hiện thuộc địa bàn quản lý mới; giữ phiếu tiếp nhận hồ sơ để theo dõi thời hạn.
+4. Chi phí dự kiến
+Công chứng văn bản thừa kế: tính theo giá trị tài sản/di sản và phí lưu giữ, sao y, soạn thảo nếu có.
+Đo đạc, trích đo, tách thửa, cấp 3 sổ: mức thu do tỉnh/thành phố quy định; thường là khoản biến động lớn nhất ngoài thuế.
+Thuế thu nhập cá nhân: thừa kế bất động sản giữa cha mẹ và con thuộc diện miễn; bố bạn nhận di sản từ ông nội nên cần làm hồ sơ chứng minh quan hệ cha–con để được miễn. Điều 18 Nghị định 253/2026/NĐ-CP
+Lệ phí trước bạ: cần kê khai để cơ quan thuế xác định diện miễn/không miễn; hồ sơ quan hệ gia đình phải đầy đủ.
+Ngoài ra có lệ phí cấp giấy chứng nhận, phí thẩm định hồ sơ (nếu địa phương thu).
+5. Lưu ý để tránh bị trả hồ sơ
+Đừng chỉ lấy chữ ký “đồng ý” của các bác. Cần đúng loại văn bản công chứng và đúng tất cả người thừa kế.
+Nếu bà nội còn sống, phải làm rõ đất là tài sản riêng của ông hay tài sản chung vợ chồng. Nếu là tài sản chung, trước hết xác định phần của bà nội; chỉ phần của ông mới là di sản.
+Kiểm tra xem có người thừa kế đã mất, mất tích, ở nước ngoài, hoặc có con riêng/con nuôi hợp pháp không; các trường hợp này làm thay đổi thành phần ký hồ sơ.
+Hãy hỏi trước bằng văn bản hoặc phiếu hướng dẫn về điều kiện tách 3 thửa. Nếu tách không đạt diện tích tối thiểu hoặc không có lối đi hợp pháp, có thể phải điều chỉnh phương án chia đất.
+Bạn nên chuẩn bị tối thiểu: sổ đỏ bản gốc, giấy chứng tử ông nội, CCCD các bên, khai sinh của bố và các giấy tờ chứng minh quan hệ, giấy đăng ký kết hôn của ông bà/bố mẹ nếu có, cùng bản dự kiến sơ đồ chia 3 thửa.
+[1]. Điều 620, 651, Luật 91/2015/QH13
+[2]. Điều 220, Luật 31/2024/QH15
+[3]. Điều 13, Thông tư 10/2024/TT-BTNMT
+[4]. Điều 18, Nghị định 253/2026/NĐ-CP</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="48" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -639,6 +756,39 @@
           <t>Kind 1 - Thủ tục quản lý đất đai</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Kết luận: Gia đình có thể làm sổ đỏ lần đầu, nhưng cần giải quyết đồng thời hai việc: xác định quyền sử dụng đất của ông bà và xác lập người thừa kế hợp pháp để đứng tên trên sổ. Vì ông bà mất đã lâu, có người con đã mất, hồ sơ thừa kế phải làm theo “các nhánh” của từng người con; người chết có con thì con họ được hưởng phần thừa kế thế vị, còn người chết không có con thì cần xem họ mất trước hay sau ông/bà để xác định phần di sản.
+1. Xác định ai là người có quyền đứng tên
+Nếu ông bà không để lại di chúc, di sản được chia theo pháp luật cho hàng thừa kế thứ nhất: vợ/chồng, cha mẹ, con của người chết. Trong thực tế của bạn, thường là các người con của ông bà; con của người con đã chết trước hoặc cùng thời điểm với ông/bà được hưởng phần mà cha/mẹ họ đáng lẽ được hưởng (thừa kế thế vị). Điều 651 Bộ luật Dân sự 2015 Điều 652 Bộ luật Dân sự 2015
+Cần làm rõ thời điểm mất của từng ông/bà và từng người con. Ví dụ: người con mất sau ông/bà thì họ đã nhận một phần di sản; khi họ mất, phần đó trở thành di sản của chính họ và được chia tiếp cho vợ/chồng, con, cha mẹ của họ. Nếu họ mất trước ông/bà và có con thì con được thừa kế thế vị. Điều 611 Bộ luật Dân sự 2015 Điều 613 Bộ luật Dân sự 2015
+Việc ông bà mất quá 30 năm không đương nhiên làm mất quyền đối với đất. Tuy nhiên, thời hiệu yêu cầu chia di sản là bất động sản là 30 năm kể từ thời điểm mở thừa kế; vì đã ở sát hoặc quá mốc này, gia đình nên thực hiện ngay và nên thống nhất bằng văn bản. Điều 623 Bộ luật Dân sự 2015
+2. Việc nên làm trước: lập văn bản thừa kế tại tổ chức công chứng
+Gia đình nên lập Văn bản thỏa thuận phân chia di sản hoặc Văn bản khai nhận di sản tại tổ chức hành nghề công chứng. Nếu mọi người thống nhất để một người hoặc một nhóm người đứng tên sổ đỏ, các đồng thừa kế ghi rõ nội dung nhường/cho phần quyền của mình trong văn bản này.
+Hồ sơ công chứng thường gồm: giấy tờ đất thời Pháp bản gốc; giấy chứng tử của ông, bà và những người con đã mất; CCCD; giấy khai sinh, đăng ký kết hôn và giấy tờ khác chứng minh quan hệ cha mẹ-con; giấy tờ chứng minh người đã mất không có con (nếu cần); giấy tờ cư trú; sơ đồ gia phả. Công chứng viên có trách nhiệm niêm yết việc thụ lý công chứng văn bản thừa kế 15 ngày. Điều 57 Luật Công chứng 2014 Điều 58 Luật Công chứng 2014
+Lưu ý: người thừa kế không thể hoặc không muốn có mặt có thể lập văn bản ủy quyền hoặc văn bản từ chối nhận di sản hợp lệ; việc từ chối phải thực hiện trước thời điểm phân chia di sản. Điều 620 Bộ luật Dân sự 2015
+3. Nộp hồ sơ cấp sổ đỏ lần đầu
+Sau khi có văn bản thừa kế đã công chứng, người được thống nhất đứng tên nộp hồ sơ đăng ký đất đai, cấp Giấy chứng nhận lần đầu tại Bộ phận Một cửa cấp xã/phường nơi có đất hoặc Chi nhánh Văn phòng đăng ký đất đai Hà Nội theo nơi tiếp nhận hồ sơ tại địa bàn.
+Hồ sơ trọng tâm gồm:
+Đơn đăng ký đất đai, tài sản gắn liền với đất và đề nghị cấp Giấy chứng nhận;
+Giấy tờ đất thời Pháp bản chính/bản sao chứng thực;
+Văn bản khai nhận hoặc thỏa thuận phân chia di sản đã công chứng;
+Giấy tờ nhân thân của người sẽ đứng tên;
+Trích đo địa chính nếu thửa đất chưa có bản đồ địa chính, ranh giới hoặc diện tích cần xác định lại;
+Chứng từ đã hoàn thành nghĩa vụ tài chính, khi cơ quan thuế thông báo.
+Giấy tờ về quyền sử dụng đất được lập trước ngày 15/10/1993 thuộc nhóm giấy tờ có thể là căn cứ cấp Giấy chứng nhận nếu xác định được đúng người sử dụng đất, ranh giới và điều kiện pháp lý của thửa đất. Điều 137 Luật Đất đai 2024 Việc đăng ký đất đai lần đầu được thực hiện theo thủ tục đăng ký đất đai, cấp Giấy chứng nhận lần đầu. Điều 18 Nghị định 101/2024/NĐ-CP
+4. Các điểm thường vướng
+Giấy tờ thời Pháp có thể ghi tên ông hoặc bà, ghi tên chủ cũ, ghi số thửa cũ hoặc diện tích không trùng hiện trạng. Cơ quan đăng ký sẽ kiểm tra nguồn gốc, quá trình sử dụng, ranh giới, quy hoạch và có thể yêu cầu xác minh/trích đo.
+Nếu có người thừa kế ở nước ngoài, mất giấy khai sinh hoặc giấy chứng tử, cần bổ sung tài liệu thay thế/xác nhận của cơ quan có thẩm quyền; đây thường là lý do hồ sơ kéo dài.
+Nếu có người con đã mất “không con cái”, cần xác định họ mất trước hay sau ông/bà và có vợ/chồng, cha/mẹ còn sống hay không; không nên tự bỏ tên nhánh thừa kế này.
+Khi gia đình đã đồng thuận, nên để toàn bộ người thuộc diện thừa kế hoặc người kế thừa của họ cùng ký văn bản công chứng. Đây là cách hạn chế rủi ro tranh chấp và việc hồ sơ cấp sổ bị yêu cầu bổ sung sau này.
+Thứ tự ngắn gọn: lập sơ đồ gia phả và thời điểm mất → thu giấy tờ chứng minh quan hệ → công chứng văn bản thừa kế → trích đo/xác minh thửa đất nếu cần → nộp hồ sơ cấp sổ đỏ lần đầu → thực hiện nghĩa vụ tài chính theo thông báo.
+[1]. Điều 611, 613, 620, 623, 651, 652, Luật 91/2015/QH13
+[2]. Điều 57, 58, Luật 53/2014/QH13
+[3]. Điều 137, Luật 31/2024/QH15
+[4]. Điều 18, Nghị định 101/2024/NĐ-CP</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="32" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
@@ -651,6 +801,20 @@
           <t>Kind 1 - Thủ tục quản lý đất đai</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Kết luận: Gia đình không thể chỉ xin cấp lại sổ đỏ mang tên bố vì bố đã mất. Cần làm thủ tục xác lập quyền thừa kế đối với thửa đất trước, sau đó người được hưởng thừa kế làm thủ tục đăng ký sang tên và được cấp Giấy chứng nhận mới; việc sổ bị cháy cần khai báo rõ khi nộp hồ sơ.
+Gia đình chuẩn bị: giấy chứng tử của bố; CCCD của mẹ và các con; giấy tờ chứng minh quan hệ (khai sinh, đăng ký kết hôn); bản photo/chụp sổ đỏ nếu còn; giấy tờ về việc cháy sổ (nếu có).
+Nếu bố có di chúc hợp pháp thì làm theo di chúc. Nếu không có di chúc, hàng thừa kế thứ nhất gồm: vợ, cha mẹ đẻ/nuôi và các con đẻ/nuôi của bố; những người này hưởng phần bằng nhau. Vì vậy, các con không thể tự để một mình mẹ đứng tên nếu chưa có văn bản thỏa thuận/phân chia hoặc từ chối nhận di sản của những người thừa kế khác. Điều 651 Bộ luật Dân sự 2015
+Các đồng thừa kế đến tổ chức công chứng tại Thanh Hóa lập “Văn bản khai nhận di sản” hoặc “Văn bản thỏa thuận phân chia di sản”. Nếu thống nhất để mẹ nhận toàn bộ đất, văn bản cần ghi rõ các người thừa kế tặng cho/thỏa thuận để mẹ nhận phần di sản đó. Thời hiệu yêu cầu chia di sản là bất động sản là 30 năm từ thời điểm bố mất. Điều 623 Bộ luật Dân sự 2015
+Sau khi có văn bản công chứng, nộp hồ sơ đăng ký biến động/sang tên tại Bộ phận một cửa cấp xã hoặc Văn phòng đăng ký đất đai/chi nhánh Văn phòng đăng ký đất đai nơi có đất ở Thanh Hóa. Hồ sơ thường gồm: đơn đăng ký biến động; văn bản thừa kế đã công chứng; giấy chứng tử; giấy tờ nhân thân; sổ đỏ còn lại hoặc văn bản trình bày việc sổ bị cháy, mất.
+Việc cấp lại/cấp mới giấy chứng nhận trong trường hợp giấy cũ bị mất, hư hỏng được thực hiện theo thủ tục đăng ký đất đai; cơ quan tiếp nhận sẽ hướng dẫn thêm việc niêm yết, xác minh nếu cần. Nghị định 101/2024/NĐ-CP
+Lưu ý: Nếu sổ đỏ là tài sản chung của bố mẹ hình thành trong thời kỳ hôn nhân, trước hết xác định phần của mẹ trong khối tài sản chung; chỉ phần thuộc bố mới chia thừa kế. Điều 33 Luật Hôn nhân và gia đình 2014
+[1]. Điều 623, 651, Luật 91/2015/QH13
+[2]. Nghị định 101/2024/NĐ-CP
+[3]. Điều 33, Luật 52/2014/QH13</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="48" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -663,6 +827,24 @@
           <t>Kind 1 - Thủ tục quản lý đất đai</t>
         </is>
       </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Kết luận: Cơ quan tư pháp không thể chỉ trả lời miệng “người đã mất thì không cấp lại”. Bạn cần yêu cầu họ tiếp nhận hồ sơ đăng ký lại khai sinh hoặc trả lời từ chối bằng văn bản; nếu không còn đủ căn cứ để đăng ký lại, con đường phù hợp là yêu cầu Tòa án xác định quan hệ cha, mẹ, con để làm thủ tục thừa kế.
+Thử thủ tục đăng ký lại khai sinh của bố bạn trước.
+Người yêu cầu có thể là người thân thích; việc đăng ký lại được thực hiện khi sổ hộ tịch và bản chính giấy khai sinh đều bị mất, đồng thời có giấy tờ/tài liệu chứng minh nội dung khai sinh. Việc bố đã mất không phải tự nó là lý do để từ chối nhận, xem xét hồ sơ. Điều 24 Luật Hộ tịch 2014 Điều 25 Luật Hộ tịch 2014 Điều 26 Luật Hộ tịch 2014
+Hồ sơ nên kèm mọi tài liệu cũ có ghi tên ông bà là cha mẹ của bố bạn: CCCD/CMND cũ, sổ hộ khẩu, lý lịch Đảng/đoàn, hồ sơ đi học, hồ sơ cán bộ, hồ sơ quân đội, giấy đăng ký kết hôn, giấy chứng tử, giấy tờ đất, hồ sơ bảo hiểm, hồ sơ khám chữa bệnh, giấy khai sinh của các anh chị em ruột của bố… Bản sao trích lục hộ tịch cũng là giấy tờ hộ tịch có giá trị như bản chính. Điều 6 Luật Hộ tịch 2014
+Nộp tại UBND cấp xã có thẩm quyền về hộ tịch nơi trước đây bố bạn đăng ký khai sinh hoặc nơi bố bạn cư trú trước khi mất. Khi nộp, đề nghị cán bộ lập giấy tiếp nhận; nếu từ chối, yêu cầu nêu rõ căn cứ và trả lời bằng văn bản để có cơ sở khiếu nại hoặc khởi kiện hành chính.
+Nếu không thể đăng ký lại khai sinh: nộp đơn tại TAND khu vực nơi bố bạn cư trú cuối cùng/yêu cầu xác định bố bạn là con của ông bà. Đây là việc dân sự thuộc thẩm quyền giải quyết của Tòa án; quyết định có hiệu lực của Tòa là căn cứ rất mạnh để công chứng khai nhận hoặc thỏa thuận phân chia di sản. Điều 29 Bộ luật Tố tụng dân sự 2015 Điều 101 Luật Hôn nhân và Gia đình 2014
+Kèm theo đơn: giấy chứng tử của bố; giấy tờ của bạn chứng minh bạn là con của bố; giấy tờ của ông bà; toàn bộ tài liệu gián tiếp nêu trên; bản tường trình của người thân, hàng xóm; và đề nghị Tòa thu thập hồ sơ lưu tại công an, trường học, cơ quan công tác, cơ quan lưu trữ. Nếu còn người thân ruột của bố, nên đề nghị họ ký xác nhận hoặc tham gia phiên họp.
+Văn phòng công chứng không có nghĩa vụ tự đi “xác minh” thay gia đình. Công chứng viên được quyền yêu cầu bổ sung tài liệu, xác minh hoặc yêu cầu giám định khi thấy cần thiết, nhưng không thể thay Tòa án xác lập quan hệ cha mẹ con khi chứng cứ hộ tịch không còn. Điều 40 Luật Công chứng 2014 Điều 57 Luật Công chứng 2014
+Lưu ý: nếu đang gần hết thời hiệu yêu cầu chia di sản thì cần nộp yêu cầu tại Tòa sớm. Thời hiệu yêu cầu chia di sản là 30 năm với bất động sản và 10 năm với động sản, tính từ thời điểm bố bạn mất. Điều 623 Bộ luật Dân sự 2015
+[1]. Điều 6, 24, 25, 26, Luật 60/2014/QH13
+[2]. Điều 29, Luật 92/2015/QH13
+[3]. Điều 101, Luật 52/2014/QH13
+[4]. Điều 40, 57, Luật 53/2014/QH13
+[5]. Điều 623, Luật 91/2015/QH13</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="48" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
@@ -673,6 +855,17 @@
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Kind 1 - Thủ tục quản lý đất đai</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Kết luận: Tầng hầm bạn mô tả có thể được ghi nhận là công trình xây dựng/tài sản gắn liền với đất khi xác minh hiện trạng, nhưng không tự động làm đất khai hoang đủ điều kiện cấp sổ đỏ lần đầu. Cơ quan có thẩm quyền sẽ xét riêng nguồn gốc, thời điểm sử dụng đất, quy hoạch, tranh chấp và việc xây dựng có hợp pháp hay không.
+Tầng hầm có móng, dầm, cột, sàn bê tông, cầu thang, bể phốt là kết cấu kiên cố; nên đề nghị đoàn xác minh lập biên bản ghi rõ: diện tích, vị trí, kết cấu, mục đích sử dụng, thời điểm xây dựng thực tế từ năm 2013 và tình trạng đang tồn tại. Thông tin về nhà/công trình, nguồn gốc sử dụng đất, thời điểm sử dụng và tranh chấp là nội dung được kiểm tra khi đăng ký đất đai lần đầu Điều 11 Thông tư 10/2024/TT-BTNMT.
+Tuy nhiên, để được cấp sổ, gia đình cần chứng minh việc sử dụng đất ổn định và không tranh chấp; đồng thời đất không thuộc trường hợp bị loại trừ như đất công, hành lang bảo vệ công trình, quy hoạch phải thu hồi hoặc khu vực không được công nhận. Nếu nguồn gốc thực tế bị xác định là lấn, chiếm nhưng đã sử dụng làm nhà ở trước 01/7/2014, không thuộc quy hoạch rừng đặc dụng/rừng phòng hộ hoặc công trình hạ tầng công cộng, vẫn có thể được xem xét cấp giấy và phải thực hiện nghĩa vụ tài chính Điều 139 Luật Đất đai 2024.
+Lưu ý quan trọng: công trình xây năm 2013 không đồng nghĩa với “hợp lệ” về xây dựng. Nếu thời điểm đó công trình thuộc diện phải có giấy phép xây dựng nhưng không có giấy phép, tầng hầm có thể vẫn được ghi nhận hiện trạng, nhưng việc chứng nhận quyền sở hữu công trình hoặc xử lý vi phạm xây dựng sẽ được xem xét riêng.
+Gia đình nên nộp/kèm: ảnh công trình qua các năm; xác nhận của người liền kề hoặc tổ dân phố; biên lai điện, nước, thuế; hồ sơ bản vẽ/biên bản xây dựng (nếu có); giấy tờ về việc khai hoang, giao đất hoặc xác nhận sử dụng đất của UBND xã. Khi biên bản xác minh ghi không đúng hiện trạng hoặc không ghi nhận tầng hầm, gia đình nên yêu cầu ghi ý kiến trực tiếp vào biên bản và giữ một bản/chụp lại.
+[1]. Điều 11, Thông tư 10/2024/TT-BTNMT
+[2]. Điều 139, Luật 31/2024/QH15</t>
         </is>
       </c>
     </row>
@@ -687,6 +880,14 @@
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Kind 1 - Thủ tục quản lý đất đai</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Kết luận: Khi làm sổ lần đầu, thời hạn nộp tiền không tính từ ngày nộp hồ sơ mà tính theo Thông báo nộp tiền của cơ quan thuế. Thông thường, khoản tiền sử dụng đất phải nộp sẽ có hạn theo pháp luật quản lý thuế; nếu được ghi nợ thì nộp theo thời hạn ghi nợ.
+Đối với hộ gia đình, cá nhân được cấp Giấy chứng nhận lần đầu, thông báo thuế phải ghi rõ: thời hạn nộp khoản tiền sử dụng đất không được ghi nợ theo pháp luật quản lý thuế và thời hạn nộp khoản được ghi nợ (nếu có) Điều 22 Nghị định 103/2024/NĐ-CP.
+Bạn nên xem chính xác dòng “thời hạn nộp tiền” trên thông báo của cơ quan thuế. Nộp quá hạn có thể bị tính tiền chậm nộp theo quy định thuế.
+[1]. Điều 22, Nghị định 103/2024/NĐ-CP</t>
         </is>
       </c>
     </row>
@@ -702,6 +903,17 @@
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Kind 1 - Thủ tục quản lý đất đai</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Kết luận: Không phải mọi hồ sơ đất đai đều bắt buộc nộp bản chính Giấy khai sinh. Bạn nên liên hệ ngay nơi đã tiếp nhận hồ sơ để đề nghị trả lại bản chính và thay bằng bản sao chứng thực hoặc bản sao kèm xuất trình bản chính đối chiếu, nếu thành phần hồ sơ không bắt buộc phải lưu bản chính.
+Khi nộp trực tiếp hồ sơ đất đai, bạn có quyền chọn nộp bản sao và xuất trình bản chính để đối chiếu, hoặc nộp bản sao đã được chứng thực; không nhất thiết phải giao luôn bản chính cho cơ quan tiếp nhận. Khoản 2 Điều 12 Nghị định 102/2024/NĐ-CP
+Bạn nên làm phiếu/đơn đề nghị rút lại bản chính Giấy khai sinh, ghi: họ tên, mã hồ sơ/ngày nộp, tên thủ tục đất đai, đề nghị nhận lại bản chính và nộp thay bằng bản sao chứng thực. Mang theo CCCD, phiếu tiếp nhận hồ sơ và bản sao chứng thực Giấy khai sinh đến Bộ phận Một cửa hoặc Văn phòng đăng ký đất đai nơi nhận hồ sơ.
+Nếu cơ quan nói không thể trả, bạn hãy yêu cầu họ trả lời rõ bằng văn bản hoặc ghi trên phiếu hướng dẫn: Giấy khai sinh là thành phần hồ sơ nào và căn cứ nào buộc phải nộp bản chính. Trường hợp bản chính thực sự cần để giải quyết thủ tục, cơ quan phải bảo quản và hoàn trả theo quy trình khi không còn cần thiết; bạn nên giữ phiếu biên nhận thể hiện đã nộp bản chính.
+Nếu bị thất lạc hoặc không thể lấy lại, bạn có thể xin bản sao trích lục khai sinh tại UBND cấp xã nơi đã đăng ký khai sinh trước đây hoặc bất kỳ UBND cấp xã có thẩm quyền khai thác dữ liệu hộ tịch. Bản sao trích lục hộ tịch có giá trị sử dụng thay cho bản chính trong giao dịch, trừ trường hợp pháp luật quy định khác. Điều 63 Luật Hộ tịch 2014
+[1]. Điều 12, Nghị định 102/2024/NĐ-CP
+[2]. Điều 63, Luật 60/2014/QH13</t>
         </is>
       </c>
     </row>
@@ -723,6 +935,38 @@
           <t>Kind 2 - Quyền, nghĩa vụ và việc sử dụng đất</t>
         </is>
       </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Kết luận: Nếu thửa 888-1 thực tế đã được chuyển nhượng cho ông Lâm và sau khi chỉnh lý địa chính được đổi thành thửa 1012, thì tại thời điểm bán căn studio vợ chồng bạn không còn quyền sử dụng thửa đất đó. Bạn cần chứng minh “chuỗi lịch sử biến động” giữa hai số thửa; giấy trích lục riêng từng hợp đồng công chứng thường chưa đủ.
+Việc cần làm ngay
+Đến Văn phòng đăng ký đất đai/Chi nhánh Văn phòng đăng ký đất đai nơi có đất, nộp đơn đề nghị:
+cung cấp thông tin, trích lục hồ sơ địa chính;
+xác nhận lịch sử biến động của thửa 888-1, tờ bản đồ 2 sang thửa 1012, tờ bản đồ 10;
+xác nhận thửa 1012 là thửa đất được cấp đổi/chỉnh lý/đánh số lại từ thửa 888-1;
+xác nhận việc đăng ký sang tên cho ông Lâm và tình trạng vợ chồng bạn đã không còn đứng tên trên thửa đất này.
+Yêu cầu quan trọng nhất là văn bản xác nhận phải ghi rõ: “thửa 888-1 tờ bản đồ số 2 và thửa 1012 tờ bản đồ số 10 là cùng một vị trí/thửa đất sau khi đo đạc, chỉnh lý hoặc thay đổi số thửa, số tờ bản đồ”. Khi biên tập lại bản đồ địa chính, số thửa có thể được đánh lại và phải có bảng tham chiếu số thửa cũ – số thửa mới Điều 18 Thông tư 26/2024/TT-BTNMT.
+Xin kèm các giấy tờ có thể hiện liên kết giữa hai thửa:
+hồ sơ cấp Giấy chứng nhận hoặc hồ sơ đăng ký biến động khi sang tên ông Lâm;
+trang biến động trên Giấy chứng nhận cũ (nếu còn);
+trích đo địa chính, mảnh trích đo, sơ đồ thửa đất;
+bảng đối chiếu số thửa cũ và số thửa mới;
+văn bản trả lời chính thức của Văn phòng đăng ký đất đai.
+Nộp cho cơ quan thuế một bộ giải trình gồm:
+hợp đồng công chứng mua thửa 888-1;
+hợp đồng công chứng bán cho ông Lâm (thửa 1012);
+bản sao Giấy chứng nhận/sơ đồ thửa đất của các giao dịch nếu có;
+đặc biệt là văn bản xác nhận lịch sử biến động của Văn phòng đăng ký đất đai;
+đơn giải trình nêu rõ: thửa 1012 không phải tài sản thứ hai, mà là chính thửa 888-1 sau đổi số thửa/tờ bản đồ và đã bán từ 5 năm trước.
+Theo quy định hiện hành, điều kiện miễn thuế là tại thời điểm chuyển nhượng căn studio, người chuyển nhượng chỉ có một nhà ở hoặc một thửa đất ở; đồng thời phải đáp ứng điều kiện thời gian sở hữu và chuyển nhượng toàn bộ nhà/đất đó Điều 19 Nghị định 253/2026/NĐ-CP. Vì vậy, trọng tâm không phải chứng minh vợ chồng bạn “chưa từng có đất”, mà chứng minh tại ngày ký bán căn studio, đất cũ đã không còn thuộc quyền sử dụng của vợ chồng bạn.
+Mẫu nội dung đơn đề nghị xác nhận
+Kính đề nghị Văn phòng đăng ký đất đai tra cứu, cung cấp trích lục hồ sơ địa chính và xác nhận lịch sử biến động đối với thửa đất số 888-1, tờ bản đồ số 2 và thửa đất số 1012, tờ bản đồ số 10.
+Đề nghị xác nhận hai số thửa nêu trên có phải cùng một thửa đất/vị trí đất trước và sau khi đo đạc, chỉnh lý hoặc thay đổi số thửa, số tờ bản đồ hay không; thời điểm vợ chồng tôi chuyển nhượng quyền sử dụng đất cho ông Lâm; và tình trạng hiện nay vợ chồng tôi không còn đăng ký quyền sử dụng đất đối với thửa đất nêu trên.
+Mục đích sử dụng: bổ sung hồ sơ giải trình miễn thuế thu nhập cá nhân khi chuyển nhượng nhà ở duy nhất.
+Nếu cơ quan thuế chỉ thông báo miệng, bạn nên đề nghị họ lập thông báo/yêu cầu bổ sung hồ sơ bằng văn bản, để biết rõ thời hạn và nội dung phải chứng minh. Nộp bộ giải trình có phiếu tiếp nhận, yêu cầu cơ quan thuế trả lời bằng văn bản về việc chấp nhận hay không chấp nhận miễn thuế.
+[1]. Điều 18, Thông tư 26/2024/TT-BTNMT
+[2]. Điều 19, Nghị định 253/2026/NĐ-CP</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="48" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
@@ -735,6 +979,12 @@
           <t>Kind 2 - Quyền, nghĩa vụ và việc sử dụng đất</t>
         </is>
       </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Kết luận: Có. Nghị quyết 254/2025/QH15 có quy định ưu đãi khi chuyển lần đầu từ đất vườn, ao hoặc đất nông nghiệp trong cùng thửa có đất ở sang đất ở; nhưng không phải “giảm 70%” cho mọi trường hợp. Với diện tích trong hạn mức đất ở, bạn chỉ nộp 30% phần chênh lệch, tức giảm tương đương 70% phần chênh lệch.
+Nghị quyết có hiệu lực từ 01/01/2026. Người đã được quyết định cho phép chuyển mục đích trong giai đoạn 01/8/2024 đến trước 01/01/2026, nếu chưa nộp tiền theo thông báo thuế,</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -745,6 +995,21 @@
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Kind 2 - Quyền, nghĩa vụ và việc sử dụng đất</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Kết luận: Nếu đất đang đồng sở hữu mà chưa xác định phần diện tích của từng người, trước hết các đồng sở hữu nên lập văn bản thỏa thuận phân chia quyền sử dụng đất. Nếu không thể thỏa thuận, một hoặc nhiều người có thể yêu cầu Tòa án chia tài sản chung.
+Việc chia chỉ thực hiện được khi thửa đất đáp ứng điều kiện tách thửa theo quy định địa phương và phù hợp quy hoạch. Các bên nên thống nhất rõ: mỗi người nhận vị trí nào, diện tích bao nhiêu m², lối đi chung (nếu có), chi phí đo đạc và nghĩa vụ thuế/phí.
+Sau khi thỏa thuận, thực hiện theo trình tự:
+Thuê đo đạc, lập bản vẽ hiện trạng và phương án chia thửa.
+Lập văn bản phân chia có công chứng/chứng thực.
+Nộp hồ sơ đăng ký biến động, tách thửa và cấp Giấy chứng nhận riêng tại cơ quan đăng ký đất đai cấp tỉnh/xã theo cơ chế tiếp nhận hồ sơ hiện hành.
+Nhận sổ riêng cho từng người nếu đủ điều kiện.
+Khi chưa chia, Giấy chứng nhận phải ghi đầy đủ tên các người có chung quyền sử dụng đất; nếu cử một người đại diện đứng tên thì phải có văn bản thỏa thuận đại diện. Điều 12 Thông tư 10/2024/TT-BTNMT
+Lưu ý: Một người không được tự ý bán, tặng cho, thế chấp “phần đất của mình” khi phần đó chưa được xác định; việc định đoạt quyền sử dụng đất chung cần sự đồng ý của các đồng sở hữu, trừ trường hợp có thỏa thuận hoặc bản án khác. Điều 218 Bộ luật Dân sự 2015
+Nếu bạn cho biết đất ở tỉnh/thành nào, tổng diện tích, loại đất và hiện có sổ chung hay chưa, có thể xác định cụ thể có đủ điều kiện tách thửa hay không.
+[1]. Điều 12, Thông tư 10/2024/TT-BTNMT</t>
         </is>
       </c>
     </row>
@@ -762,6 +1027,30 @@
           <t>Kind 2 - Quyền, nghĩa vụ và việc sử dụng đất</t>
         </is>
       </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Kết luận: Bố mẹ bạn chỉ nên làm thủ tục tặng cho sau khi đo đạc, xác định rõ phần đất thực tế tăng thêm 400 m² có thuộc quyền sử dụng hợp pháp hay không. Phần 900 m² đã ghi trên sổ có thể tặng cho nếu đủ điều kiện; còn 400 m² chênh lệch không tự động được công nhận và không nên đưa vào hợp đồng tặng cho khi chưa được cơ quan đăng ký đất đai xác nhận.
+1. Xử lý diện tích thực tế 1.300 m²
+Sổ năm 2004 đang xác nhận tổng diện tích 900 m² gồm 250 m² đất ở/lâu dài và 650 m² đất vườn. Việc thực tế đang sử dụng khoảng 1.300 m² cần đo đạc địa chính chính thức, xác định ranh giới với các hộ liền kề và đặc biệt là mốc hành lang, đất công ven suối.
+Nếu 400 m² tăng thêm chỉ là sai số đo đạc, ranh giới sử dụng ổn định, không tranh chấp, không lấn đất công/hành lang suối: gia đình có thể đề nghị đăng ký biến động hoặc cấp đổi sổ theo số liệu đo đạc thực tế.
+Nếu phần tăng thêm là đất ven suối, đất do Nhà nước quản lý, đất thuộc hành lang bảo vệ nguồn nước hoặc có dấu hiệu lấn chiếm: không được công nhận để tặng cho; có thể phải trả lại phần đất đó.
+“Giáp suối” không đồng nghĩa toàn bộ đất gia đình đang dùng là hợp pháp. Cần kiểm tra chỉ giới hành lang bảo vệ nguồn nước và hồ sơ địa chính tại địa phương trước.
+Người sử dụng đất chỉ được tặng cho khi có Giấy chứng nhận, đất không tranh chấp, không bị kê biên, còn thời hạn sử dụng và không bị áp dụng biện pháp khẩn cấp tạm thời Điều 45 Luật Đất đai 2024.
+2. Tặng cho hai người con: cần tách thửa hay không?
+Nếu bố mẹ muốn mỗi người con đứng tên một phần đất riêng: phải làm thủ tục tách thửa trước hoặc tách thửa đồng thời với thủ tục tặng cho. Diện tích, kích thước từng thửa sau tách phải đáp ứng quy định đang áp dụng tại Hà Nội; phần đất ở và đất vườn cần được thể hiện rõ theo từng thửa.
+Nếu bố mẹ muốn hai con cùng đứng tên chung toàn bộ thửa đất: không nhất thiết tách thửa; có thể lập hợp đồng tặng cho quyền sử dụng đất cho hai người con theo tỷ lệ cụ thể, ví dụ mỗi người 1/2.
+Do đất có hai loại mục đích sử dụng, khi chia nên xác định rõ: mỗi con được nhận bao nhiêu m² đất ở và bao nhiêu m² đất vườn. Không nên tự ghi toàn bộ diện tích là đất ở vì đất vườn không tự chuyển thành đất ở.
+3. Trình tự nên thực hiện
+Liên hệ Văn phòng đăng ký đất đai/chi nhánh nơi có đất để đề nghị trích đo địa chính, kiểm tra ranh giới, diện tích chênh lệch và tình trạng đất ven suối.
+Nếu đủ điều kiện, làm thủ tục cấp đổi/chỉnh lý Giấy chứng nhận theo kết quả đo đạc; nếu muốn chia riêng thì lập hồ sơ tách thửa.
+Sau khi diện tích hợp pháp được xác định, bố mẹ và các con lập hợp đồng tặng cho tại tổ chức công chứng.
+Nộp hồ sơ đăng ký biến động sang tên tại cơ quan đăng ký đất đai. Hồ sơ cơ bản gồm: sổ gốc, hợp đồng tặng cho đã công chứng, giấy tờ nhân thân, giấy tờ chứng minh quan hệ cha mẹ–con và hồ sơ tách thửa nếu có.
+4. Thuế, phí
+Tặng cho quyền sử dụng đất giữa cha mẹ và con thuộc trường hợp được miễn thuế thu nhập cá nhân và miễn lệ phí trước bạ, nếu hồ sơ chứng minh đúng quan hệ cha mẹ–con. Gia đình vẫn có thể phải nộp phí đo đạc, phí thẩm định, phí cấp/cấp đổi sổ và nghĩa vụ tài chính nếu được công nhận thêm diện tích đất ngoài sổ.
+Lưu ý quan trọng: Không ký hợp đồng tặng cho theo diện tích “khoảng 1.300 m²” khi sổ mới ghi 900 m². Hợp đồng chỉ nên ghi theo diện tích hợp pháp trên Giấy chứng nhận hoặc theo hồ sơ đo đạc đã được cơ quan có thẩm quyền chấp nhận.
+[1]. Điều 45, Luật 31/2024/QH15</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="64" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -777,6 +1066,21 @@
           <t>Kind 2 - Quyền, nghĩa vụ và việc sử dụng đất</t>
         </is>
       </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Kết luận: Không thể khẳng định cán bộ, nhân viên được tự bán nhà/đất cho người ngoài đơn vị. Việc bán chỉ hợp pháp khi người đó đã được Nhà nước hoặc tổ chức giao/bán hợp pháp và đã có quyền sở hữu nhà, quyền sử dụng đất riêng; đồng thời không bị hạn chế chuyển nhượng theo quyết định giao đất, hồ sơ dự án hoặc loại nhà ở.
+Nếu đất được Nhà nước giao trực tiếp cho tổ chức kinh tế để bố trí chỗ ở nội bộ, thì tổ chức là bên có quyền đối với đất. Cán bộ, nhân viên chỉ được bố trí ở, thuê hoặc thuê mua thường chưa đương nhiên có quyền bán cho người khác. Người tự ý bán khi chưa được cấp Giấy chứng nhận hoặc chưa được tổ chức chuyển quyền hợp pháp thì giao dịch có nguy cơ vô hiệu.
+Chỉ có thể bán ra ngoài đơn vị khi, tối thiểu:
+Người bán đã đứng tên Giấy chứng nhận đối với nhà ở/quyền sử dụng đất hoặc đủ điều kiện được cấp Giấy chứng nhận;
+Nhà, đất không có tranh chấp, không bị kê biên, còn thời hạn sử dụng và không thuộc trường hợp pháp luật cấm/chưa cho chuyển nhượng;
+Việc bán phù hợp với quy định của dự án và văn bản giao đất; nếu là nhà ở xã hội, nhà công vụ, nhà thuộc tài sản công hoặc nhà được ưu đãi thì có hạn chế riêng;
+Hợp đồng chuyển nhượng được công chứng/chứng thực theo quy định và đăng ký biến động. Điều 45 Luật Đất đai 2024 Điều 164 Luật Nhà ở 2023
+Cần phân biệt: nếu đây là nhà công vụ hoặc nhà do cơ quan/đơn vị bố trí để ở trong thời gian công tác thì không được mua bán như tài sản riêng. Điều 32 Luật Nhà ở 2023
+Bạn nên kiểm tra 3 giấy tờ: quyết định Nhà nước giao đất cho tổ chức, hợp đồng/quyết định phân nhà cho cán bộ nhân viên, và Giấy chứng nhận của căn nhà/đất. Chỉ cần một trong các giấy tờ này ghi “không được chuyển nhượng”, “chỉ để bố trí nội bộ”, hoặc chưa tách/cấp sổ riêng thì không nên giao dịch với người ngoài đơn vị.
+[1]. Điều 45, Luật 31/2024/QH15
+[2]. Điều 32, 164, Luật 27/2023/QH15</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="64" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
@@ -788,6 +1092,18 @@
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Kind 2 - Quyền, nghĩa vụ và việc sử dụng đất</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Kết luận: Chồng bạn không thể dùng giấy ủy quyền để tự chuyển sổ đất từ chủ đất sang chính tên chồng bạn. Tuy nhiên, chồng bạn có thể đại diện chủ đất để ký hợp đồng chuyển nhượng hoặc tặng cho cho bạn, nếu giấy ủy quyền còn hiệu lực và ghi rõ quyền định đoạt/chuyển nhượng/tặng cho; việc này cần bảo đảm không trái phạm vi ủy quyền và ý chí của chủ đất.
+Người được ủy quyền là người đại diện cho chủ đất, không phải là chủ sở hữu đất. Vì vậy, chồng bạn không được xác lập giao dịch mà bên chuyển là chủ đất (do chồng đại diện) và bên nhận lại chính là chồng bạn; đây là giao dịch với chính mình, có nguy cơ vô hiệu nếu không có sự đồng ý/ủy quyền hợp lệ từ chủ đất. Điều 141 Bộ luật Dân sự 2015
+Nếu chuyển sang tên bạn, chồng bạn là người đại diện bên chuyển, còn bạn là bên nhận nên về nguyên tắc không phải giao dịch “với chính mình”. Nhưng cần kiểm tra kỹ giấy ủy quyền có cho phép chồng bạn: ký hợp đồng chuyển nhượng/tặng cho; nộp hồ sơ; kê khai và nộp thuế, phí; làm thủ tục sang tên hay không. Nếu giấy chỉ ghi “quản lý”, “làm thủ tục hành chính” thì chưa đủ để bán/tặng cho.
+Cách an toàn nhất là để chủ đất trực tiếp ký hợp đồng tặng cho/chuyển nhượng cho bạn tại tổ chức công chứng. Nếu chủ đất không thể ký, nên lập lại văn bản ủy quyền công chứng, ghi rõ chồng bạn được ký hợp đồng chuyển nhượng hoặc tặng cho quyền sử dụng đất cho bạn, giá trị giao dịch (nếu mua bán), quyền nộp hồ sơ và nhận kết quả.
+Đất phải có Giấy chứng nhận, không tranh chấp, không bị kê biên, còn thời hạn sử dụng và không bị áp dụng biện pháp khẩn cấp tạm thời mới đủ điều kiện chuyển nhượng/tặng cho. Điều 45 Luật Đất đai 2024 Hợp đồng chuyển nhượng hoặc tặng cho quyền sử dụng đất phải được công chứng hoặc chứng thực. Điều 27 Luật Đất đai 2024
+Lưu ý thêm: nếu bạn và chồng đã kết hôn, đất đứng tên riêng bạn nhưng tiền mua là tài sản chung vợ chồng thì vẫn có thể phát sinh tranh chấp về tài sản chung. Nếu muốn là tài sản riêng của bạn, nên chọn hình thức tặng cho riêng bạn và ghi rõ trong hợp đồng: “tặng cho riêng bà…; không nhập vào tài sản chung vợ chồng”.
+[1]. Điều 141, Luật 91/2015/QH13
+[2]. Điều 27, 45, Luật 31/2024/QH15</t>
         </is>
       </c>
     </row>
@@ -802,6 +1118,23 @@
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Kind 2 - Quyền, nghĩa vụ và việc sử dụng đất</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Kết luận: Có hợp đồng ủy quyền công chứng chưa chắc người được ủy quyền đã tự ký bán đất được. Văn phòng công chứng thường từ chối nếu văn bản ủy quyền không ghi thật rõ quyền ký hợp đồng chuyển nhượng, nhận tiền, nộp hồ sơ sang tên; hoặc nếu đất là tài sản chung vợ chồng, quyền ủy quyền đã hết/hủy, hay có dấu hiệu rủi ro giao dịch.
+Với đất đứng tên 2 đồng sở hữu, việc bán phải có sự đồng ý của cả hai. Người ở xa có thể ủy quyền, nhưng người được ủy quyền chỉ được thực hiện đúng phạm vi đã ghi trong giấy ủy quyền; giao dịch vượt phạm vi này không ràng buộc người ủy quyền, trừ trường hợp được chấp nhận sau đó Điều 141 Bộ luật Dân sự 2015.
+Bạn kiểm tra hợp đồng ủy quyền có các nội dung cụ thể như sau không:
+Quyền “thay mặt ký hợp đồng chuyển nhượng quyền sử dụng đất/quyền sở hữu nhà ở” với bên mua;
+Thông tin chính xác thửa đất, số Giấy chứng nhận;
+Quyền thỏa thuận giá, phương thức thanh toán, ký hồ sơ công chứng, hồ sơ thuế và sang tên;
+Quyền nhận tiền chuyển nhượng hoặc chỉ định tiền phải chuyển thẳng vào tài khoản của người ủy quyền;
+Thời hạn ủy quyền còn hiệu lực.
+Hợp đồng ủy quyền về nguyên tắc là sự thỏa thuận để bên được ủy quyền thực hiện công việc nhân danh bên ủy quyền; nếu không ghi thời hạn thì thường có hiệu lực 01 năm kể từ ngày xác lập Điều 562 Bộ luật Dân sự 2015 Điều 563 Bộ luật Dân sự 2015. Việc ủy quyền có thể chấm dứt khi hết hạn, công việc hoàn thành, một bên đơn phương chấm dứt, hoặc người ủy quyền/người được ủy quyền chết, mất năng lực hành vi dân sự... Điều 569 Bộ luật Dân sự 2015.
+Ngoài ra, nếu một hoặc cả hai phần đất là tài sản chung vợ chồng, dù sổ chỉ ghi tên một người, công chứng viên có thể yêu cầu vợ/chồng cùng ký hoặc có văn bản xác nhận/ủy quyền hợp lệ. Việc định đoạt bất động sản là tài sản chung phải có sự thỏa thuận bằng văn bản của vợ chồng Điều 35 Luật Hôn nhân và gia đình 2014.
+Cách xử lý thực tế: mang bản gốc giấy ủy quyền đến đúng văn phòng công chứng đang từ chối và yêu cầu họ nêu rõ lý do từ chối bằng văn bản. Nếu lý do là thiếu phạm vi ủy quyền, người ở xa cần lập lại hoặc bổ sung ủy quyền tại tổ chức công chứng nơi mình đang có mặt; không nhất thiết phải về nơi có đất. Văn bản mới nên ghi đúng các quyền nêu trên, đặc biệt là quyền ký hợp đồng chuyển nhượng.
+[1]. Điều 141, 562, 563, 569, Luật 91/2015/QH13
+[2]. Điều 35, Luật 52/2014/QH13</t>
         </is>
       </c>
     </row>
@@ -826,6 +1159,26 @@
           <t>Kind 2 - Quyền, nghĩa vụ và việc sử dụng đất</t>
         </is>
       </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Kết luận: Căn nhà mua năm 2023, khi vợ chồng chưa ly hôn, về nguyên tắc vẫn bị suy đoán là tài sản chung vợ chồng, dù người chồng đã bỏ đi từ năm 2000. Người vợ không nên tự bán một mình nếu chưa có căn cứ pháp lý xác lập nhà là tài sản riêng hoặc quyền sở hữu riêng; cách an toàn nhất là yêu cầu Tòa án giải quyết tình trạng hôn nhân và tài sản.
+Việc chồng không còn chung sống, không chu cấp, vợ tự nuôi con và tự tích góp tiền mua nhà là chứng cứ rất quan trọng. Tuy nhiên, tài sản hình thành trong thời kỳ hôn nhân thường được coi là tài sản chung, trừ khi vợ chứng minh đó là tài sản riêng; khi không chứng minh được nguồn gốc thì pháp luật cũng coi là tài sản chung. Điều 33 Luật Hôn nhân và gia đình 2014
+Tài sản riêng có thể là tài sản mỗi người có trước hôn nhân; được thừa kế riêng, tặng cho riêng; hoặc tài sản hình thành từ tài sản riêng. Người nào cho rằng nhà là tài sản riêng thì có nghĩa vụ đưa ra chứng cứ chứng minh. Điều 43 Luật Hôn nhân và gia đình 2014 Điều 44 Luật Hôn nhân và gia đình 2014
+Hướng xử lý phù hợp:
+Nếu còn liên lạc được với chồng:
+Hai người có thể lập văn bản thỏa thuận xác nhận căn nhà là tài sản riêng của vợ hoặc thỏa thuận chia tài sản chung trong thời kỳ hôn nhân. Văn bản liên quan đến bất động sản phải được công chứng theo quy định. Sau đó đăng ký biến động để ghi nhận quyền sở hữu riêng của vợ trước khi bán. Điều 38 Luật Hôn nhân và gia đình 2014 Điều 47 Luật Hôn nhân và gia đình 2014
+Nếu chồng biệt tích, không rõ còn sống hay ở đâu:
+Không thể chỉ làm “giấy cam kết tài sản riêng” tại văn phòng công chứng để tự bán nhà, vì công chứng viên thường sẽ yêu cầu chữ ký/chấp thuận của chồng hoặc bản án, quyết định của Tòa án. Việc tự bán có thể bị tranh chấp, yêu cầu hủy giao dịch sau này.
+Người vợ cần thu thập chứng cứ chồng vắng mặt liên tục: xác nhận của Công an/UBND cấp xã nơi cư trú cuối cùng, xác nhận tổ dân phố, lời khai người thân, tài liệu tìm kiếm, tin nhắn hoặc giấy tờ khác. Nếu chồng đã biệt tích từ năm 2000 và không có tin tức xác thực, có thể yêu cầu Tòa án tuyên bố chồng mất tích; điều kiện là đã biệt tích 02 năm liền trở lên dù đã áp dụng đầy đủ biện pháp thông báo, tìm kiếm. Điều 68 Bộ luật Dân sự 2015
+Sau khi có quyết định tuyên bố mất tích:
+Người vợ có thể yêu cầu Tòa án cho ly hôn với người chồng bị tuyên bố mất tích. Khi ly hôn, đề nghị Tòa án giải quyết luôn căn nhà: công nhận là tài sản riêng nếu chứng minh được toàn bộ nguồn tiền riêng, hoặc chia tài sản chung và giao nhà cho vợ sở hữu theo phần Tòa án xác định. Khoản 2 Điều 56 Luật Hôn nhân và gia đình 2014 Điều 59 Luật Hôn nhân và gia đình 2014
+Hồ sơ chứng minh nguồn tiền mua nhà nên chuẩn bị gồm: hợp đồng mua bán/chuyển nhượng năm 2023; giấy chứng nhận; sao kê ngân hàng; giấy nhận tiền bán tài sản riêng (nếu có); chứng cứ thu nhập, kinh doanh, vay tiền; giấy vay và chứng từ trả nợ; xác nhận chồng không chung sống, không đóng góp; chứng cứ vợ một mình nuôi con, quản lý tài sản từ năm 2000.
+Lưu ý quan trọng: Việc căn nhà đứng tên một mình người vợ chưa đủ để khẳng định đó là tài sản riêng. Với nhà là tài sản chung, việc bán phải có sự thỏa thuận bằng văn bản của cả vợ và chồng; nếu không, giao dịch có rủi ro rất lớn cho cả người bán và người mua. Điều 35 Luật Hôn nhân và gia đình 2014
+Khi đã có bản án/quyết định có hiệu lực xác định nhà thuộc riêng vợ hoặc giao toàn bộ nhà cho vợ, người vợ mang giấy tờ đó cùng giấy chứng nhận nhà đất, giấy tờ nhân thân đến tổ chức công chứng để ký hợp đồng chuyển nhượng; sau đó người mua làm thủ tục đăng ký sang tên theo quy định đất đai.
+[1]. Điều 33, 35, 38, 43, 44, 47, 56, 59, Luật 52/2014/QH13
+[2]. Điều 68, Luật 91/2015/QH13</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="64" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -836,6 +1189,28 @@
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Kind 2 - Quyền, nghĩa vụ và việc sử dụng đất</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Kết luận: Ba bạn chưa thể tự làm sổ riêng hoặc chuyển nhượng phần hơn 300 m² chỉ dựa vào vi bằng và việc đang đứng chung trên sổ của ông A. Vì ông A đã mất, trước hết cần xác định giao dịch năm 2000 có chứng cứ gì, những người thừa kế của ông A phải hoàn tất thủ tục thừa kế; sau đó họ mới có thể cùng ba bạn ký thủ tục hợp thức hóa, tách thửa và sang tên nếu đất đủ điều kiện.
+Vi bằng chỉ là tài liệu ghi nhận sự kiện, hành vi hoặc việc giao nhận tiền/giấy tờ (nếu có); không tự thay thế hợp đồng chuyển nhượng quyền sử dụng đất được công chứng hoặc chứng thực. Hợp đồng chuyển nhượng đất của cá nhân về nguyên tắc phải công chứng/chứng thực Điều 27 Luật Đất đai 2024.
+1. Việc cần làm đầu tiên: xác minh hồ sơ
+Cần thu thập: vi bằng bản gốc, giấy tay mua bán (nếu có), chứng cứ trả tiền, giấy giao đất, người làm chứng, biên lai thuế, xác nhận quản lý/sử dụng ổn định, ảnh hiện trạng và bản gốc Giấy chứng nhận đang mang tên ông A.
+Đồng thời kiểm tra: diện tích 300 m² nằm ở vị trí nào trên thửa đất chung; có đang tranh chấp/quy hoạch/kê biên không; đất có đủ diện tích tối thiểu để tách thửa theo quy định nơi có đất không. Vì bạn chưa nêu tỉnh/thành phố nên chưa thể kết luận diện tích này có tách được hay không.
+2. Người thừa kế của ông A phải tham gia
+Khi ông A mất, quyền sử dụng đất đứng tên ông A trở thành di sản. Những người thừa kế hợp pháp của ông A cần lập văn bản khai nhận hoặc thỏa thuận phân chia di sản tại tổ chức công chứng; nếu không có di chúc thì xác định theo hàng thừa kế thứ nhất gồm vợ/chồng, cha mẹ, con của ông A Điều 651 Bộ luật Dân sự 2015.
+Sau đó có hai hướng:
+Hướng thuận lợi nhất: toàn bộ người thừa kế thừa nhận việc ông A đã bán phần đất này cho ba bạn, cùng ký văn bản thỏa thuận và hợp đồng chuyển nhượng/công nhận giao dịch tại tổ chức công chứng. Sau đó thực hiện tách thửa, đăng ký biến động và cấp Giấy chứng nhận cho ba bạn.
+Nếu có người không hợp tác hoặc tranh chấp: ba bạn cần khởi kiện tại Tòa án yêu cầu công nhận giao dịch/chuyển quyền hoặc giải quyết tranh chấp quyền sử dụng đất. Vi bằng, giấy giao nhận tiền, quá trình sử dụng đất công khai ổn định là chứng cứ quan trọng, nhưng không bảo đảm chắc chắn Tòa sẽ công nhận vì còn phụ thuộc nội dung giấy tờ, thời điểm giao dịch, việc giao đất thực tế và ý kiến các thừa kế.
+3. Tách thửa rồi mới sang tên riêng
+Chỉ khi người có quyền hợp pháp đối với thửa đất ký hồ sơ chuyển nhượng và thửa đất đủ điều kiện tách, ba bạn mới có thể được cấp sổ riêng cho phần hơn 300 m². Điều kiện cơ bản để chuyển nhượng gồm: có Giấy chứng nhận, đất không tranh chấp, không bị kê biên, còn thời hạn sử dụng và không bị áp dụng biện pháp khẩn cấp tạm thời Điều 45 Luật Đất đai 2024.
+Do đất là đất trồng cây lâu năm, nếu ba bạn hoặc các con muốn xây nhà thì phải kiểm tra quy hoạch và làm thủ tục chuyển mục đích sử dụng đất trước hoặc đồng thời theo quy định; không nên tự xây khi đất vẫn là đất nông nghiệp.
+4. Ba bạn có thể chuyển cho các con khi nào?
+An toàn nhất là: hoàn tất sổ riêng đứng tên ba bạn trước, rồi ba bạn lập hợp đồng tặng cho hoặc chuyển nhượng cho các con, có công chứng/chứng thực và đăng ký sang tên. Không nên “bán tiếp” bằng giấy tay/vi bằng khi ba bạn chưa có sổ riêng, vì sẽ làm chuỗi giấy tờ phức tạp và tăng nguy cơ tranh chấp.
+Nếu các con là người dự kiến nhận đất, có thể cân nhắc để toàn bộ người thừa kế ông A chuyển nhượng trực tiếp cho các con, nhưng chỉ nên làm khi tất cả người thừa kế đã thống nhất rõ ràng và cơ quan đăng ký đất đai chấp nhận hồ sơ.
+[1]. Điều 27, 45, Luật 31/2024/QH15
+[2]. Điều 651, Luật 91/2015/QH13</t>
         </is>
       </c>
     </row>
